--- a/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C8">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,7 +750,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>13</v>
@@ -761,7 +761,7 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -807,16 +807,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2">
-        <v>74.5</v>
+        <v>74.8</v>
       </c>
       <c r="D2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2">
-        <v>77.5</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +827,13 @@
         <v>27</v>
       </c>
       <c r="C3">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="D3">
         <v>23</v>
       </c>
       <c r="E3">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
     </row>
   </sheetData>
